--- a/Result/checksun_type/資服.xlsx
+++ b/Result/checksun_type/資服.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>72.5</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>72.56</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>76.49</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>76.48999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>13865.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>6521.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>6521</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6483.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>21480.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>21480.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-418.6888189420579</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>13865</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13865.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>71.88</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>72.56</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>76.7</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>76.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2571.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4450.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4450.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5653.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>25516.7</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>25516.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1216.68766164667</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2571</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2571.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>71.34</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>72.65</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>76.88</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>72.65000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>76.88</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3855.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>6143.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>6143.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5750.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>26372.9</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>26372.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1103.16144902302</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3855</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3855.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>71.36</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>72.83</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>76.93</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>72.83</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>76.93000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>9753.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6941.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>6941.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5791.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>26625.5</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>26625.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1039.153950666985</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>9753</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>9753.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>71.46000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>73.18</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>77.05</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>77.05</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>2561.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>5857.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>5857.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5323.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>26894.5</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>26894.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1542.530597634543</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>2561</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2561.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>71.72</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>73.57</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>77.13</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>73.56999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>77.13</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3514.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>6445.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>6445.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>5397.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>27392.76</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>27392.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1435.978286244104</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3514</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3514.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>72.03999999999999</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>73.92</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>77.15</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>77.15000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>11034.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>6855.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>6855.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>5439.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>27408.92</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>27408.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1334.582902606189</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>11034</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>11034.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>72.38000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>74.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>77.17</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>77.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>7847.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5357.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>5357</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>4769.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>27235.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>27235.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1947.782965173234</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7847</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7847.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>72.32000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>74.34</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>77.13</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>77.13</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>4331.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>4641.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>4641.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4327.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>27108.7</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>27108.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-2412.755091512823</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>4331</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>4331.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>72.56</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>74.52</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>77.12</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>74.52</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>77.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>5502.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>4788.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>4788.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>5092.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>27277.66</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>27277.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-2614.116875872493</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>5502</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>5502.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>72.64000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>74.7</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>77.11</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>77.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>5565.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4349.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4349</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5652.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>27276.18</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>27276.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-2933.879536533719</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>5565</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5565.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>211.4</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>220.6</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>232.46</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>232.46</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>15442.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>10237.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>10237.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>23088.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>24917.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>24917.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3777.605565963258</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>15442</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>15442.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>210.1</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>221.28</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>233.27</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>221.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>233.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>10103.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>14680.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>14680.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>25007.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>26045.02</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>26045.02</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3802.177114171132</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>10103</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>10103.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>209.5</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>222.25</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>234.22</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>222.25</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>234.22</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1057.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>19947.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>19947.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>38168.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>26368.16</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>26368.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-3129.451571819125</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1057</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1057.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>210.2</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>223.38</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>235.11</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>223.38</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>235.11</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>11095.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>34015.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>34015.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>42020.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>26892.78</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>26892.78</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-1087.434669465576</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>11095</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>11095.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>212.9</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>224.65</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>236.08</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>224.65</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>236.08</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>13490.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>35699.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>35699.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>42992.7</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>27949.52</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>27949.52</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>793.0692863775548</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>13490</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>13490.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>215.1</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>225.72</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>237.05</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>225.72</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>237.05</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>37659.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>35939.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>35939.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>42817.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>28693.26</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>28693.26</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>3194.572463068551</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>37659</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>37659.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>218.3</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>227.18</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>238.06</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>227.18</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>238.06</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>36438.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>35334.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>35334.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>41566.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>29520.94</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>29520.94</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>3921.663698946089</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>36438</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>36438.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>221.2</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>228.45</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>239.0</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>228.45</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>239</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>71395.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>56389.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>56389.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>39348.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>29021.08</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>29021.08</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>4951.127475237357</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>71395</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>71395.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>223.3</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>229.3</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>239.78</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>229.3</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>239.78</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>19516.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>50026.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>50026.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>33091.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>28127.16</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>28127.16</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>2499.571174394976</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>19516</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>19516.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>225.1</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>230.02</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>240.53</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>230.02</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>240.53</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>14690.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>50285.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>50285.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>32852.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>28490.92</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>28490.92</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>4466.541774106037</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>14690</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>14690.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>226.7</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>230.52</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>241.29</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>230.52</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>241.29</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>34634.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>49695.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>49695.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>32777.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>29976.72</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>29976.72</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>7634.051853189478</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>34634</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>34634.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>127.1</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>129.52</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>135.77</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>129.52</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>135.77</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>5885.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>4913.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>4913.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>9574.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>9511.3</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>9511.299999999999</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-859.9149679335142</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>5885</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>5885.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>126.4</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>129.72</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>136.17</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>129.72</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>136.17</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>4210.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>6538.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>6538</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>9700.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>9957.02</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>9957.02</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-851.4500188526199</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>4210</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>4210.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>126.4</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>130.02</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>136.62</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>130.02</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>136.62</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>2218.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>8348.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>8348.799999999999</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>9820.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>10311.8</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>10311.8</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-629.4840194923199</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>2218</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>2218.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>127.0</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>130.3</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>137.03</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>137.03</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>6198.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>9740.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>9740.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>11050.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>10746.7</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>10746.7</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-76.47959113859542</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>6198</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>6198.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>128.3</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>130.7</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>137.37</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>137.37</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>6055.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>11431.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>11431.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>11045.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>10673.4</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>10673.4</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>289.8295776216764</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>6055</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>6055.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>129.1</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>131.1</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>137.69</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>131.1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>137.69</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>14009.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>14235.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>14235.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>10887.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>10665.32</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>10665.32</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>818.0987623641486</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>14009</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>14009.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>130.1</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>138.02</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>138.02</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>13264.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>12863.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>12863.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>10152.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>10437.88</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>10437.88</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>691.3369276261019</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>13264</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>13264.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>130.7</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>131.72</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>138.32</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>131.72</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>138.32</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>9177.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>11291.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>11291.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>9761.8</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>10259.3</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>10259.3</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>565.3794162993872</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>9177</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>9177.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>130.8</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>131.93</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>138.57</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>131.93</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>138.57</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>14654.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>12359.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>12359.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>9213.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>10181.52</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>10181.52</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>803.1408495362484</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>14654</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>14654.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>130.3</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>131.98</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>138.77</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>131.98</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>138.77</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>20075.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>10658.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>10658.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>8431.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>10026.46</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>10026.46</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>527.295009534042</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>20075</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>20075.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>130.3</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>132.15</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>139.03</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>132.15</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>139.03</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>7147.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>7539.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>7539</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>6953.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>9713.12</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>9713.120000000001</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-466.4238693810394</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>7147</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>7147.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>91.6</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>92.84</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>90.54</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>92.84</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>90.54000000000001</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>34018.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>23269.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>23269.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>25375.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>20196.08</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>20196.08</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>1302.273244028765</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>34018</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>34018.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>92.14</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>93.08</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>90.52</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>90.52</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>27194.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>20304.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>20304.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>23617.0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>19939.46</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>19939.46</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>466.0883970251343</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>27194</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>27194.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>92.4</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>93.21</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>90.52</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>90.52</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>14096.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>21669.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>21669.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>22575.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>19566.56</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>19566.56</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-13.96454144522795</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>14096</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>14096.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>93.32</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>93.34</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>90.49</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>90.48999999999999</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>13827.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>29288.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>29288.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>22115.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>19553.94</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>19553.94</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>704.1014229344364</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>13827</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>13827.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>93.5</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>93.33</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>90.44</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>90.44</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>27211.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>29946.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>29946.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>22395.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>19406.42</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>19406.42</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>1733.584892657724</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>27211</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>27211.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>93.05999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>93.46</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>90.35</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>90.34999999999999</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>19195.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>27481.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>27481</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>20789.9</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>19031.22</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>19031.22</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>1708.361817524648</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>19195</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>19195.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>93.61999999999999</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>93.53</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>90.33</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>90.33</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>34019.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>26929.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>26929.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>19751.6</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>18957.08</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>18957.08</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>2470.173073851518</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>34019</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>34019.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>94.25999999999999</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>93.36</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>90.29</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>90.29000000000001</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>52192.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>23481.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>23481</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>17978.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>18406.26</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>18406.26</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>1881.968687395205</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>52192</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>52192.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>93.9</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>92.75</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>90.13</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>90.13</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>17117.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>14942.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>14942.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>14564.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>17526.18</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>17526.18</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-972.6436035207844</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>17117</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>17117.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>93.94</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>92.31</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>90.04</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>90.04000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>14882.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>14844.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>14844.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>14755.4</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>17368.58</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>17368.58</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-1257.888176132168</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>14882</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>14882.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>94.05999999999999</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>91.9</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>89.97</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>89.97</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>16437.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>14098.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>14098.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>14361.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>17251.7</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>17251.7</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-1380.991559286567</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>16437</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>16437.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
